--- a/05_Figures/HRvLR/S01_Volcano/c_data/s01_volcano.xlsx
+++ b/05_Figures/HRvLR/S01_Volcano/c_data/s01_volcano.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="279">
   <si>
     <t>sheet</t>
   </si>
@@ -423,7 +423,7 @@
     <t>set_tests</t>
   </si>
   <si>
-    <t>02_HRvLR_groups/03_Set_Contrasts/c_data/set_tests.rds</t>
+    <t>03_Group_comparisons/HRvLR/03_Set_Contrasts/c_data/set_tests.rds</t>
   </si>
   <si>
     <t>b928dfb75f0631b92e8ffaf819778f86</t>
@@ -534,12 +534,24 @@
     <t>Github (Dustyn-T-Lewis/enrichVolcano@d3fed631f4ae95e01bd61137699313f8de5cc86e)</t>
   </si>
   <si>
+    <t>evaluate</t>
+  </si>
+  <si>
+    <t>1.0.5</t>
+  </si>
+  <si>
     <t>farver</t>
   </si>
   <si>
     <t>2.1.2</t>
   </si>
   <si>
+    <t>fastmap</t>
+  </si>
+  <si>
+    <t>1.2.0</t>
+  </si>
+  <si>
     <t>foreach</t>
   </si>
   <si>
@@ -603,6 +615,18 @@
     <t>1.1.4</t>
   </si>
   <si>
+    <t>htmltools</t>
+  </si>
+  <si>
+    <t>0.5.9</t>
+  </si>
+  <si>
+    <t>htmlwidgets</t>
+  </si>
+  <si>
+    <t>1.6.4</t>
+  </si>
+  <si>
     <t>IRanges</t>
   </si>
   <si>
@@ -615,6 +639,18 @@
     <t>1.0.14</t>
   </si>
   <si>
+    <t>jsonlite</t>
+  </si>
+  <si>
+    <t>2.0.0</t>
+  </si>
+  <si>
+    <t>knitr</t>
+  </si>
+  <si>
+    <t>1.51</t>
+  </si>
+  <si>
     <t>labeling</t>
   </si>
   <si>
@@ -624,9 +660,6 @@
     <t>lifecycle</t>
   </si>
   <si>
-    <t>1.0.5</t>
-  </si>
-  <si>
     <t>magrittr</t>
   </si>
   <si>
@@ -645,6 +678,12 @@
     <t>1.5.0</t>
   </si>
   <si>
+    <t>otel</t>
+  </si>
+  <si>
+    <t>0.2.0</t>
+  </si>
+  <si>
     <t>pillar</t>
   </si>
   <si>
@@ -720,6 +759,12 @@
     <t>CRAN (R 4.6.1)</t>
   </si>
   <si>
+    <t>rmarkdown</t>
+  </si>
+  <si>
+    <t>2.31</t>
+  </si>
+  <si>
     <t>rprojroot</t>
   </si>
   <si>
@@ -799,6 +844,18 @@
   </si>
   <si>
     <t>3.0.2</t>
+  </si>
+  <si>
+    <t>xfun</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>yaml</t>
+  </si>
+  <si>
+    <t>2.3.12</t>
   </si>
 </sst>
 </file>
@@ -3064,7 +3121,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -3336,7 +3393,7 @@
         <v>185</v>
       </c>
       <c r="B25" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="C25" t="s">
         <v>141</v>
@@ -3344,10 +3401,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B26" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C26" t="s">
         <v>141</v>
@@ -3355,10 +3412,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B27" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C27" t="s">
         <v>141</v>
@@ -3394,7 +3451,7 @@
         <v>195</v>
       </c>
       <c r="C30" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -3438,7 +3495,7 @@
         <v>203</v>
       </c>
       <c r="C34" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -3490,7 +3547,7 @@
         <v>212</v>
       </c>
       <c r="B39" t="s">
-        <v>213</v>
+        <v>172</v>
       </c>
       <c r="C39" t="s">
         <v>141</v>
@@ -3498,10 +3555,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>213</v>
+      </c>
+      <c r="B40" t="s">
         <v>214</v>
-      </c>
-      <c r="B40" t="s">
-        <v>215</v>
       </c>
       <c r="C40" t="s">
         <v>141</v>
@@ -3509,10 +3566,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
+        <v>215</v>
+      </c>
+      <c r="B41" t="s">
         <v>216</v>
-      </c>
-      <c r="B41" t="s">
-        <v>217</v>
       </c>
       <c r="C41" t="s">
         <v>141</v>
@@ -3520,10 +3577,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
+        <v>217</v>
+      </c>
+      <c r="B42" t="s">
         <v>218</v>
-      </c>
-      <c r="B42" t="s">
-        <v>219</v>
       </c>
       <c r="C42" t="s">
         <v>141</v>
@@ -3531,10 +3588,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
+        <v>219</v>
+      </c>
+      <c r="B43" t="s">
         <v>220</v>
-      </c>
-      <c r="B43" t="s">
-        <v>221</v>
       </c>
       <c r="C43" t="s">
         <v>141</v>
@@ -3542,10 +3599,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
+        <v>221</v>
+      </c>
+      <c r="B44" t="s">
         <v>222</v>
-      </c>
-      <c r="B44" t="s">
-        <v>223</v>
       </c>
       <c r="C44" t="s">
         <v>141</v>
@@ -3553,10 +3610,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
+        <v>223</v>
+      </c>
+      <c r="B45" t="s">
         <v>224</v>
-      </c>
-      <c r="B45" t="s">
-        <v>225</v>
       </c>
       <c r="C45" t="s">
         <v>141</v>
@@ -3564,10 +3621,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
+        <v>225</v>
+      </c>
+      <c r="B46" t="s">
         <v>226</v>
-      </c>
-      <c r="B46" t="s">
-        <v>227</v>
       </c>
       <c r="C46" t="s">
         <v>141</v>
@@ -3575,10 +3632,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
+        <v>227</v>
+      </c>
+      <c r="B47" t="s">
         <v>228</v>
-      </c>
-      <c r="B47" t="s">
-        <v>229</v>
       </c>
       <c r="C47" t="s">
         <v>141</v>
@@ -3586,21 +3643,21 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
+        <v>229</v>
+      </c>
+      <c r="B48" t="s">
         <v>230</v>
       </c>
-      <c r="B48" t="s">
-        <v>231</v>
-      </c>
       <c r="C48" t="s">
-        <v>232</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B49" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C49" t="s">
         <v>141</v>
@@ -3608,21 +3665,21 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B50" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C50" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B51" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C51" t="s">
         <v>141</v>
@@ -3630,10 +3687,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B52" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C52" t="s">
         <v>141</v>
@@ -3641,10 +3698,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B53" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C53" t="s">
         <v>141</v>
@@ -3652,10 +3709,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B54" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C54" t="s">
         <v>141</v>
@@ -3663,21 +3720,21 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
+        <v>243</v>
+      </c>
+      <c r="B55" t="s">
+        <v>244</v>
+      </c>
+      <c r="C55" t="s">
         <v>245</v>
-      </c>
-      <c r="B55" t="s">
-        <v>246</v>
-      </c>
-      <c r="C55" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
+        <v>246</v>
+      </c>
+      <c r="B56" t="s">
         <v>247</v>
-      </c>
-      <c r="B56" t="s">
-        <v>248</v>
       </c>
       <c r="C56" t="s">
         <v>141</v>
@@ -3685,10 +3742,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
+        <v>248</v>
+      </c>
+      <c r="B57" t="s">
         <v>249</v>
-      </c>
-      <c r="B57" t="s">
-        <v>250</v>
       </c>
       <c r="C57" t="s">
         <v>141</v>
@@ -3696,13 +3753,13 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
+        <v>250</v>
+      </c>
+      <c r="B58" t="s">
         <v>251</v>
       </c>
-      <c r="B58" t="s">
-        <v>167</v>
-      </c>
       <c r="C58" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -3710,7 +3767,7 @@
         <v>252</v>
       </c>
       <c r="B59" t="s">
-        <v>211</v>
+        <v>253</v>
       </c>
       <c r="C59" t="s">
         <v>141</v>
@@ -3718,10 +3775,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B60" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C60" t="s">
         <v>141</v>
@@ -3729,10 +3786,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B61" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C61" t="s">
         <v>141</v>
@@ -3740,10 +3797,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B62" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C62" t="s">
         <v>141</v>
@@ -3751,12 +3808,122 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B63" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C63" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>262</v>
+      </c>
+      <c r="B64" t="s">
+        <v>263</v>
+      </c>
+      <c r="C64" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>264</v>
+      </c>
+      <c r="B65" t="s">
+        <v>265</v>
+      </c>
+      <c r="C65" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>266</v>
+      </c>
+      <c r="B66" t="s">
+        <v>167</v>
+      </c>
+      <c r="C66" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>267</v>
+      </c>
+      <c r="B67" t="s">
+        <v>224</v>
+      </c>
+      <c r="C67" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>268</v>
+      </c>
+      <c r="B68" t="s">
+        <v>184</v>
+      </c>
+      <c r="C68" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>269</v>
+      </c>
+      <c r="B69" t="s">
+        <v>270</v>
+      </c>
+      <c r="C69" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>271</v>
+      </c>
+      <c r="B70" t="s">
+        <v>272</v>
+      </c>
+      <c r="C70" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>273</v>
+      </c>
+      <c r="B71" t="s">
+        <v>274</v>
+      </c>
+      <c r="C71" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>275</v>
+      </c>
+      <c r="B72" t="s">
+        <v>276</v>
+      </c>
+      <c r="C72" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>277</v>
+      </c>
+      <c r="B73" t="s">
+        <v>278</v>
+      </c>
+      <c r="C73" t="s">
         <v>141</v>
       </c>
     </row>

--- a/05_Figures/HRvLR/S01_Volcano/c_data/s01_volcano.xlsx
+++ b/05_Figures/HRvLR/S01_Volcano/c_data/s01_volcano.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="262">
   <si>
     <t>sheet</t>
   </si>
@@ -423,7 +423,7 @@
     <t>set_tests</t>
   </si>
   <si>
-    <t>03_Group_comparisons/HRvLR/03_Set_Contrasts/c_data/set_tests.rds</t>
+    <t>03_Group_comparisons/HRvLR/c_data/03_set_tests.rds</t>
   </si>
   <si>
     <t>b928dfb75f0631b92e8ffaf819778f86</t>
@@ -534,132 +534,99 @@
     <t>Github (Dustyn-T-Lewis/enrichVolcano@d3fed631f4ae95e01bd61137699313f8de5cc86e)</t>
   </si>
   <si>
-    <t>evaluate</t>
+    <t>farver</t>
+  </si>
+  <si>
+    <t>2.1.2</t>
+  </si>
+  <si>
+    <t>foreach</t>
+  </si>
+  <si>
+    <t>1.5.2</t>
+  </si>
+  <si>
+    <t>generics</t>
+  </si>
+  <si>
+    <t>0.1.4</t>
+  </si>
+  <si>
+    <t>GetoptLong</t>
+  </si>
+  <si>
+    <t>1.1.1</t>
+  </si>
+  <si>
+    <t>ggforce</t>
+  </si>
+  <si>
+    <t>0.5.0</t>
+  </si>
+  <si>
+    <t>ggplot2</t>
+  </si>
+  <si>
+    <t>4.0.3</t>
+  </si>
+  <si>
+    <t>ggrepel</t>
+  </si>
+  <si>
+    <t>0.9.8</t>
+  </si>
+  <si>
+    <t>GlobalOptions</t>
+  </si>
+  <si>
+    <t>glue</t>
+  </si>
+  <si>
+    <t>1.8.1</t>
+  </si>
+  <si>
+    <t>gtable</t>
+  </si>
+  <si>
+    <t>0.3.6</t>
+  </si>
+  <si>
+    <t>here</t>
+  </si>
+  <si>
+    <t>1.0.2</t>
+  </si>
+  <si>
+    <t>hms</t>
+  </si>
+  <si>
+    <t>1.1.4</t>
+  </si>
+  <si>
+    <t>IRanges</t>
+  </si>
+  <si>
+    <t>2.46.0</t>
+  </si>
+  <si>
+    <t>iterators</t>
+  </si>
+  <si>
+    <t>1.0.14</t>
+  </si>
+  <si>
+    <t>labeling</t>
+  </si>
+  <si>
+    <t>0.4.3</t>
+  </si>
+  <si>
+    <t>lifecycle</t>
   </si>
   <si>
     <t>1.0.5</t>
   </si>
   <si>
-    <t>farver</t>
-  </si>
-  <si>
-    <t>2.1.2</t>
-  </si>
-  <si>
-    <t>fastmap</t>
-  </si>
-  <si>
-    <t>1.2.0</t>
-  </si>
-  <si>
-    <t>foreach</t>
-  </si>
-  <si>
-    <t>1.5.2</t>
-  </si>
-  <si>
-    <t>generics</t>
-  </si>
-  <si>
-    <t>0.1.4</t>
-  </si>
-  <si>
-    <t>GetoptLong</t>
-  </si>
-  <si>
-    <t>1.1.1</t>
-  </si>
-  <si>
-    <t>ggforce</t>
-  </si>
-  <si>
-    <t>0.5.0</t>
-  </si>
-  <si>
-    <t>ggplot2</t>
-  </si>
-  <si>
-    <t>4.0.3</t>
-  </si>
-  <si>
-    <t>ggrepel</t>
-  </si>
-  <si>
-    <t>0.9.8</t>
-  </si>
-  <si>
-    <t>GlobalOptions</t>
-  </si>
-  <si>
-    <t>glue</t>
-  </si>
-  <si>
-    <t>1.8.1</t>
-  </si>
-  <si>
-    <t>gtable</t>
-  </si>
-  <si>
-    <t>0.3.6</t>
-  </si>
-  <si>
-    <t>here</t>
-  </si>
-  <si>
-    <t>1.0.2</t>
-  </si>
-  <si>
-    <t>hms</t>
-  </si>
-  <si>
-    <t>1.1.4</t>
-  </si>
-  <si>
-    <t>htmltools</t>
-  </si>
-  <si>
-    <t>0.5.9</t>
-  </si>
-  <si>
-    <t>htmlwidgets</t>
-  </si>
-  <si>
-    <t>1.6.4</t>
-  </si>
-  <si>
-    <t>IRanges</t>
-  </si>
-  <si>
-    <t>2.46.0</t>
-  </si>
-  <si>
-    <t>iterators</t>
-  </si>
-  <si>
-    <t>1.0.14</t>
-  </si>
-  <si>
-    <t>jsonlite</t>
-  </si>
-  <si>
-    <t>2.0.0</t>
-  </si>
-  <si>
-    <t>knitr</t>
-  </si>
-  <si>
-    <t>1.51</t>
-  </si>
-  <si>
-    <t>labeling</t>
-  </si>
-  <si>
-    <t>0.4.3</t>
-  </si>
-  <si>
-    <t>lifecycle</t>
-  </si>
-  <si>
     <t>magrittr</t>
   </si>
   <si>
@@ -678,12 +645,6 @@
     <t>1.5.0</t>
   </si>
   <si>
-    <t>otel</t>
-  </si>
-  <si>
-    <t>0.2.0</t>
-  </si>
-  <si>
     <t>pillar</t>
   </si>
   <si>
@@ -759,12 +720,6 @@
     <t>CRAN (R 4.6.1)</t>
   </si>
   <si>
-    <t>rmarkdown</t>
-  </si>
-  <si>
-    <t>2.31</t>
-  </si>
-  <si>
     <t>rprojroot</t>
   </si>
   <si>
@@ -844,12 +799,6 @@
   </si>
   <si>
     <t>3.0.2</t>
-  </si>
-  <si>
-    <t>xfun</t>
-  </si>
-  <si>
-    <t>0.57</t>
   </si>
   <si>
     <t>yaml</t>
@@ -3121,7 +3070,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -3393,7 +3342,7 @@
         <v>185</v>
       </c>
       <c r="B25" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="C25" t="s">
         <v>141</v>
@@ -3401,10 +3350,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
+        <v>186</v>
+      </c>
+      <c r="B26" t="s">
         <v>187</v>
-      </c>
-      <c r="B26" t="s">
-        <v>188</v>
       </c>
       <c r="C26" t="s">
         <v>141</v>
@@ -3412,10 +3361,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
+        <v>188</v>
+      </c>
+      <c r="B27" t="s">
         <v>189</v>
-      </c>
-      <c r="B27" t="s">
-        <v>180</v>
       </c>
       <c r="C27" t="s">
         <v>141</v>
@@ -3451,7 +3400,7 @@
         <v>195</v>
       </c>
       <c r="C30" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -3495,7 +3444,7 @@
         <v>203</v>
       </c>
       <c r="C34" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -3547,7 +3496,7 @@
         <v>212</v>
       </c>
       <c r="B39" t="s">
-        <v>172</v>
+        <v>213</v>
       </c>
       <c r="C39" t="s">
         <v>141</v>
@@ -3555,10 +3504,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B40" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C40" t="s">
         <v>141</v>
@@ -3566,10 +3515,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B41" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C41" t="s">
         <v>141</v>
@@ -3577,10 +3526,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B42" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C42" t="s">
         <v>141</v>
@@ -3588,10 +3537,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B43" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C43" t="s">
         <v>141</v>
@@ -3599,10 +3548,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B44" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C44" t="s">
         <v>141</v>
@@ -3610,10 +3559,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B45" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C45" t="s">
         <v>141</v>
@@ -3621,10 +3570,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B46" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C46" t="s">
         <v>141</v>
@@ -3632,10 +3581,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B47" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C47" t="s">
         <v>141</v>
@@ -3643,21 +3592,21 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B48" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C48" t="s">
-        <v>141</v>
+        <v>232</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B49" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C49" t="s">
         <v>141</v>
@@ -3665,21 +3614,21 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B50" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C50" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B51" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C51" t="s">
         <v>141</v>
@@ -3687,10 +3636,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B52" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C52" t="s">
         <v>141</v>
@@ -3698,10 +3647,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B53" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C53" t="s">
         <v>141</v>
@@ -3709,10 +3658,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B54" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C54" t="s">
         <v>141</v>
@@ -3720,21 +3669,21 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B55" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C55" t="s">
-        <v>245</v>
+        <v>141</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B56" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C56" t="s">
         <v>141</v>
@@ -3742,10 +3691,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B57" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C57" t="s">
         <v>141</v>
@@ -3753,13 +3702,13 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B58" t="s">
-        <v>251</v>
+        <v>167</v>
       </c>
       <c r="C58" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -3767,7 +3716,7 @@
         <v>252</v>
       </c>
       <c r="B59" t="s">
-        <v>253</v>
+        <v>211</v>
       </c>
       <c r="C59" t="s">
         <v>141</v>
@@ -3775,10 +3724,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B60" t="s">
-        <v>255</v>
+        <v>180</v>
       </c>
       <c r="C60" t="s">
         <v>141</v>
@@ -3786,10 +3735,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B61" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C61" t="s">
         <v>141</v>
@@ -3797,10 +3746,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B62" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C62" t="s">
         <v>141</v>
@@ -3808,10 +3757,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B63" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C63" t="s">
         <v>141</v>
@@ -3819,111 +3768,12 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B64" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" t="s">
-        <v>264</v>
-      </c>
-      <c r="B65" t="s">
-        <v>265</v>
-      </c>
-      <c r="C65" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" t="s">
-        <v>266</v>
-      </c>
-      <c r="B66" t="s">
-        <v>167</v>
-      </c>
-      <c r="C66" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" t="s">
-        <v>267</v>
-      </c>
-      <c r="B67" t="s">
-        <v>224</v>
-      </c>
-      <c r="C67" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" t="s">
-        <v>268</v>
-      </c>
-      <c r="B68" t="s">
-        <v>184</v>
-      </c>
-      <c r="C68" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" t="s">
-        <v>269</v>
-      </c>
-      <c r="B69" t="s">
-        <v>270</v>
-      </c>
-      <c r="C69" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" t="s">
-        <v>271</v>
-      </c>
-      <c r="B70" t="s">
-        <v>272</v>
-      </c>
-      <c r="C70" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" t="s">
-        <v>273</v>
-      </c>
-      <c r="B71" t="s">
-        <v>274</v>
-      </c>
-      <c r="C71" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" t="s">
-        <v>275</v>
-      </c>
-      <c r="B72" t="s">
-        <v>276</v>
-      </c>
-      <c r="C72" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" t="s">
-        <v>277</v>
-      </c>
-      <c r="B73" t="s">
-        <v>278</v>
-      </c>
-      <c r="C73" t="s">
         <v>141</v>
       </c>
     </row>
